--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.30_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03080901155237131</v>
+        <v>0.01691679776450127</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03080901155237131</v>
+        <v>0.01691679776450127</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.03061411362998835</v>
+        <v>0.01679177502459634</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03061411362998835</v>
+        <v>0.01679177502459634</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03030350118107193</v>
+        <v>0.01659605416607761</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03030350118107193</v>
+        <v>0.01659605416607761</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02991323980853898</v>
+        <v>0.01635896462924314</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02991323980853898</v>
+        <v>0.01635896462924314</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02953857266722335</v>
+        <v>0.01613057267565626</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02953857266722335</v>
+        <v>0.01613057267565626</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02926761508104729</v>
+        <v>0.01597389118460034</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02926761508104729</v>
+        <v>0.01597389118460034</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02917403289108132</v>
+        <v>0.01592845853662641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02917403289108132</v>
+        <v>0.01592845853662641</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02934466876742806</v>
+        <v>0.01604067058972919</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02934466876742806</v>
+        <v>0.01604067058972919</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02991886962372717</v>
+        <v>0.01638868643663695</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02991886962372717</v>
+        <v>0.01638868643663695</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03088069952925257</v>
+        <v>0.016962438879356</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03088069952925257</v>
+        <v>0.016962438879356</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03234285887913271</v>
+        <v>0.01782297733282607</v>
       </c>
       <c r="C12" t="n">
-        <v>0.03234285887913271</v>
+        <v>0.01782297733282607</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03437836042754288</v>
+        <v>0.01901033887058945</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03437836042754288</v>
+        <v>0.01901033887058945</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03703587805341237</v>
+        <v>0.02054980999559818</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03703587805341237</v>
+        <v>0.02054980999559818</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04032859835456896</v>
+        <v>0.02244678072237527</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04032859835456896</v>
+        <v>0.02244678072237527</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04422973514123071</v>
+        <v>0.02469267075144673</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04422973514123071</v>
+        <v>0.02469267075144673</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.04867594565967884</v>
+        <v>0.02722331796393691</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04867594565967884</v>
+        <v>0.02722331796393691</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05352165446079776</v>
+        <v>0.02997731121266382</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05352165446079776</v>
+        <v>0.02997731121266382</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.05866398031227141</v>
+        <v>0.03288420120127173</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05866398031227141</v>
+        <v>0.03288420120127173</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06405966932579293</v>
+        <v>0.03591689562892782</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06405966932579293</v>
+        <v>0.03591689562892782</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.06957373831361927</v>
+        <v>0.03899318459614411</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06957373831361927</v>
+        <v>0.03899318459614411</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.07512305231481732</v>
+        <v>0.04207048032589226</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07512305231481732</v>
+        <v>0.04207048032589226</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.08067023254011142</v>
+        <v>0.04512869512477344</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08067023254011142</v>
+        <v>0.04512869512477344</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.08613136558898216</v>
+        <v>0.04812532714551756</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08613136558898216</v>
+        <v>0.04812532714551756</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.09170317018354844</v>
+        <v>0.05117779523174477</v>
       </c>
       <c r="C25" t="n">
-        <v>0.09170317018354844</v>
+        <v>0.05117779523174477</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0976925600030281</v>
+        <v>0.05446634406664203</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0976925600030281</v>
+        <v>0.05446634406664203</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1041091489160017</v>
+        <v>0.05800245868554219</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1041091489160017</v>
+        <v>0.05800245868554219</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1109368312214449</v>
+        <v>0.06178129601105908</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1109368312214449</v>
+        <v>0.06178129601105908</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1181390334714457</v>
+        <v>0.0657846223963595</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1181390334714457</v>
+        <v>0.0657846223963595</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1259128098360255</v>
+        <v>0.0701219064440835</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1259128098360255</v>
+        <v>0.0701219064440835</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1336870385704549</v>
+        <v>0.07447633022089227</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1336870385704549</v>
+        <v>0.07447633022089227</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
